--- a/outputs/54242.xlsx
+++ b/outputs/54242.xlsx
@@ -197,27 +197,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
